--- a/Parts_Inventory_Report_26_03_2026.xlsx
+++ b/Parts_Inventory_Report_26_03_2026.xlsx
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Export Date: 2026-03-26 08:21:14</t>
+          <t>Export Date: 2026-03-26 09:01:50</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F185" s="4" t="n">
         <v>5</v>
